--- a/dist/templates/Code_on_Wages/Form VI - Muster Roll.xlsx
+++ b/dist/templates/Code_on_Wages/Form VI - Muster Roll.xlsx
@@ -427,7 +427,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,37 +449,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFEBF3FB"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor rgb="FFDDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFEBF3FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF3FB"/>
-        <bgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -539,104 +515,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -670,7 +642,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFDDEBF7"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -684,13 +656,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEBF3FB"/>
-      <rgbColor rgb="FFE2EFDA"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCCCC"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -895,777 +867,777 @@
   <dimension ref="A1:AO24"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="5" style="0" width="3.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="36" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="5" style="1" width="3.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="36" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+      <c r="AD1" s="2"/>
+      <c r="AE1" s="2"/>
+      <c r="AF1" s="2"/>
+      <c r="AG1" s="2"/>
+      <c r="AH1" s="2"/>
+      <c r="AI1" s="2"/>
+      <c r="AJ1" s="2"/>
+      <c r="AK1" s="2"/>
+      <c r="AL1" s="2"/>
+      <c r="AM1" s="2"/>
+      <c r="AN1" s="2"/>
+      <c r="AO1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="Q9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="R9" s="6" t="s">
+      <c r="R9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="S9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="T9" s="6" t="s">
+      <c r="T9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="U9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="V9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="W9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="X9" s="6" t="s">
+      <c r="X9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="Y9" s="6" t="s">
+      <c r="Y9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="Z9" s="6" t="s">
+      <c r="Z9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="AA9" s="6" t="s">
+      <c r="AA9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="AB9" s="6" t="s">
+      <c r="AB9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AC9" s="6" t="s">
+      <c r="AC9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AD9" s="6" t="s">
+      <c r="AD9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AE9" s="6" t="s">
+      <c r="AE9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="AF9" s="6" t="s">
+      <c r="AF9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AG9" s="6" t="s">
+      <c r="AG9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="AH9" s="6" t="s">
+      <c r="AH9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AI9" s="6" t="n">
+      <c r="AI9" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="AJ9" s="6" t="s">
+      <c r="AJ9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AK9" s="6" t="s">
+      <c r="AK9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AL9" s="6" t="s">
+      <c r="AL9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AM9" s="6" t="s">
+      <c r="AM9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="AN9" s="6" t="s">
+      <c r="AN9" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="O10" s="10" t="s">
+      <c r="O10" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="10" t="s">
+      <c r="P10" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="Q10" s="10" t="s">
+      <c r="Q10" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="R10" s="10" t="s">
+      <c r="R10" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="S10" s="10" t="s">
+      <c r="S10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="T10" s="10" t="s">
+      <c r="T10" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="U10" s="10" t="s">
+      <c r="U10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="V10" s="10" t="s">
+      <c r="V10" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="W10" s="10" t="s">
+      <c r="W10" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="X10" s="10" t="s">
+      <c r="X10" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="Y10" s="10" t="s">
+      <c r="Y10" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="Z10" s="10" t="s">
+      <c r="Z10" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AA10" s="10" t="s">
+      <c r="AA10" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="AB10" s="10" t="s">
+      <c r="AB10" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="AC10" s="10" t="s">
+      <c r="AC10" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="AD10" s="10" t="s">
+      <c r="AD10" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="AE10" s="10" t="s">
+      <c r="AE10" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="AF10" s="10" t="s">
+      <c r="AF10" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="AG10" s="10" t="s">
+      <c r="AG10" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="AH10" s="10" t="s">
+      <c r="AH10" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="AI10" s="10" t="s">
+      <c r="AI10" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="AJ10" s="8" t="s">
+      <c r="AJ10" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AK10" s="8" t="s">
+      <c r="AK10" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AL10" s="11" t="s">
+      <c r="AL10" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="AM10" s="12" t="s">
+      <c r="AM10" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="AN10" s="10" t="s">
+      <c r="AN10" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="16"/>
+    <row r="11" s="18" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
       <c r="X11" s="17"/>
       <c r="Y11" s="17"/>
-      <c r="Z11" s="15"/>
-      <c r="AA11" s="15"/>
-      <c r="AB11" s="15"/>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="15"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
       <c r="AE11" s="17"/>
       <c r="AF11" s="17"/>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="15"/>
-      <c r="AI11" s="15"/>
-      <c r="AJ11" s="11"/>
-      <c r="AK11" s="11"/>
-      <c r="AL11" s="11"/>
-      <c r="AM11" s="11"/>
-      <c r="AN11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="14"/>
+      <c r="AK11" s="14"/>
+      <c r="AL11" s="14"/>
+      <c r="AM11" s="14"/>
+      <c r="AN11" s="14"/>
+    </row>
+    <row r="12" s="18" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
       <c r="X12" s="17"/>
       <c r="Y12" s="17"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
-      <c r="AB12" s="15"/>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
       <c r="AE12" s="17"/>
       <c r="AF12" s="17"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="15"/>
-      <c r="AI12" s="15"/>
-      <c r="AJ12" s="11"/>
-      <c r="AK12" s="11"/>
-      <c r="AL12" s="11"/>
-      <c r="AM12" s="11"/>
-      <c r="AN12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="14"/>
+      <c r="AK12" s="14"/>
+      <c r="AL12" s="14"/>
+      <c r="AM12" s="14"/>
+      <c r="AN12" s="14"/>
+    </row>
+    <row r="13" s="18" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
       <c r="J13" s="17"/>
       <c r="K13" s="17"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
       <c r="X13" s="17"/>
       <c r="Y13" s="17"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
       <c r="AE13" s="17"/>
       <c r="AF13" s="17"/>
-      <c r="AG13" s="15"/>
-      <c r="AH13" s="15"/>
-      <c r="AI13" s="15"/>
-      <c r="AJ13" s="11"/>
-      <c r="AK13" s="11"/>
-      <c r="AL13" s="11"/>
-      <c r="AM13" s="11"/>
-      <c r="AN13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="14"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+      <c r="AM13" s="14"/>
+      <c r="AN13" s="14"/>
+    </row>
+    <row r="14" s="18" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
       <c r="J14" s="17"/>
       <c r="K14" s="17"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="16"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
       <c r="Q14" s="17"/>
       <c r="R14" s="17"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
       <c r="X14" s="17"/>
       <c r="Y14" s="17"/>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
-      <c r="AB14" s="15"/>
-      <c r="AC14" s="15"/>
-      <c r="AD14" s="15"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
       <c r="AE14" s="17"/>
       <c r="AF14" s="17"/>
-      <c r="AG14" s="15"/>
-      <c r="AH14" s="15"/>
-      <c r="AI14" s="15"/>
-      <c r="AJ14" s="11"/>
-      <c r="AK14" s="11"/>
-      <c r="AL14" s="11"/>
-      <c r="AM14" s="11"/>
-      <c r="AN14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="14"/>
+      <c r="AK14" s="14"/>
+      <c r="AL14" s="14"/>
+      <c r="AM14" s="14"/>
+      <c r="AN14" s="14"/>
+    </row>
+    <row r="15" s="18" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
       <c r="R15" s="17"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
       <c r="X15" s="17"/>
       <c r="Y15" s="17"/>
-      <c r="Z15" s="15"/>
-      <c r="AA15" s="15"/>
-      <c r="AB15" s="15"/>
-      <c r="AC15" s="15"/>
-      <c r="AD15" s="15"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
       <c r="AE15" s="17"/>
       <c r="AF15" s="17"/>
-      <c r="AG15" s="15"/>
-      <c r="AH15" s="15"/>
-      <c r="AI15" s="15"/>
-      <c r="AJ15" s="11"/>
-      <c r="AK15" s="11"/>
-      <c r="AL15" s="11"/>
-      <c r="AM15" s="11"/>
-      <c r="AN15" s="11"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="14"/>
+      <c r="AK15" s="14"/>
+      <c r="AL15" s="14"/>
+      <c r="AM15" s="14"/>
+      <c r="AN15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="21" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="X16" s="20"/>
-      <c r="Y16" s="20"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
-      <c r="AE16" s="20"/>
-      <c r="AF16" s="20"/>
-      <c r="AG16" s="20"/>
-      <c r="AH16" s="20"/>
-      <c r="AI16" s="20"/>
-      <c r="AJ16" s="22" t="n">
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="19"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
+      <c r="AC16" s="19"/>
+      <c r="AD16" s="19"/>
+      <c r="AE16" s="19"/>
+      <c r="AF16" s="19"/>
+      <c r="AG16" s="19"/>
+      <c r="AH16" s="19"/>
+      <c r="AI16" s="19"/>
+      <c r="AJ16" s="21" t="n">
         <f aca="false">SUM(AJ10:AJ15)</f>
         <v>0</v>
       </c>
-      <c r="AK16" s="22" t="n">
+      <c r="AK16" s="21" t="n">
         <f aca="false">SUM(AK10:AK15)</f>
         <v>0</v>
       </c>
-      <c r="AL16" s="22" t="n">
+      <c r="AL16" s="21" t="n">
         <f aca="false">SUM(AL10:AL15)</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="22" t="n">
+      <c r="AM16" s="21" t="n">
         <f aca="false">SUM(AM10:AM15)</f>
         <v>0</v>
       </c>
-      <c r="AN16" s="20"/>
+      <c r="AN16" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="23"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="23"/>
-      <c r="Q18" s="23"/>
-      <c r="R18" s="23"/>
-      <c r="S18" s="23"/>
-      <c r="T18" s="23"/>
-      <c r="U18" s="23"/>
-      <c r="V18" s="23"/>
-      <c r="W18" s="23"/>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
-      <c r="AA18" s="23"/>
-      <c r="AB18" s="23"/>
-      <c r="AC18" s="23"/>
-      <c r="AD18" s="23"/>
-      <c r="AE18" s="23"/>
-      <c r="AF18" s="23"/>
-      <c r="AG18" s="23"/>
-      <c r="AH18" s="23"/>
-      <c r="AI18" s="23"/>
-      <c r="AJ18" s="23"/>
-      <c r="AK18" s="23"/>
-      <c r="AL18" s="23"/>
-      <c r="AM18" s="23"/>
-      <c r="AN18" s="23"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="22"/>
+      <c r="AF18" s="22"/>
+      <c r="AG18" s="22"/>
+      <c r="AH18" s="22"/>
+      <c r="AI18" s="22"/>
+      <c r="AJ18" s="22"/>
+      <c r="AK18" s="22"/>
+      <c r="AL18" s="22"/>
+      <c r="AM18" s="22"/>
+      <c r="AN18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
-      <c r="N19" s="23"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="23"/>
-      <c r="Q19" s="23"/>
-      <c r="R19" s="23"/>
-      <c r="S19" s="23"/>
-      <c r="T19" s="23"/>
-      <c r="U19" s="23"/>
-      <c r="V19" s="23"/>
-      <c r="W19" s="23"/>
-      <c r="X19" s="23"/>
-      <c r="Y19" s="23"/>
-      <c r="Z19" s="23"/>
-      <c r="AA19" s="23"/>
-      <c r="AB19" s="23"/>
-      <c r="AC19" s="23"/>
-      <c r="AD19" s="23"/>
-      <c r="AE19" s="23"/>
-      <c r="AF19" s="23"/>
-      <c r="AG19" s="23"/>
-      <c r="AH19" s="23"/>
-      <c r="AI19" s="23"/>
-      <c r="AJ19" s="23"/>
-      <c r="AK19" s="23"/>
-      <c r="AL19" s="23"/>
-      <c r="AM19" s="23"/>
-      <c r="AN19" s="23"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="22"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+      <c r="AG19" s="22"/>
+      <c r="AH19" s="22"/>
+      <c r="AI19" s="22"/>
+      <c r="AJ19" s="22"/>
+      <c r="AK19" s="22"/>
+      <c r="AL19" s="22"/>
+      <c r="AM19" s="22"/>
+      <c r="AN19" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="N21" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="AA21" s="3" t="s">
+      <c r="AA21" s="4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="N22" s="24" t="s">
+      <c r="N22" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="AA22" s="24" t="s">
+      <c r="AA22" s="23" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
+      <c r="A23" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="N23" s="24" t="s">
+      <c r="N23" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="AA23" s="24" t="s">
+      <c r="AA23" s="23" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="N24" s="24" t="s">
+      <c r="N24" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="AA24" s="24" t="s">
+      <c r="AA24" s="23" t="s">
         <v>96</v>
       </c>
     </row>
